--- a/streamlit_app/secondary_dataset.xlsx
+++ b/streamlit_app/secondary_dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jamal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DataThon\datathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E18252-3DDE-4EDF-B88E-71AF4489493A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B728DF47-8687-4B2F-9BAC-3CFCB2BF648D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>District</t>
   </si>
@@ -82,97 +82,103 @@
     <t>Student Teacher Ratio</t>
   </si>
   <si>
-    <t>Bagalkote</t>
-  </si>
-  <si>
-    <t>Bengaluru Urban</t>
-  </si>
-  <si>
-    <t>Bengaluru Rural</t>
-  </si>
-  <si>
-    <t>Belagavi</t>
-  </si>
-  <si>
-    <t>Ballari</t>
-  </si>
-  <si>
-    <t>Bidar</t>
-  </si>
-  <si>
-    <t>Vijayapura</t>
-  </si>
-  <si>
-    <t>Chamarajanagar</t>
-  </si>
-  <si>
-    <t>Chikkaballapur</t>
-  </si>
-  <si>
-    <t>Chikkamagaluru</t>
-  </si>
-  <si>
-    <t>Chitradurga</t>
-  </si>
-  <si>
-    <t>Dakshina Kannada</t>
-  </si>
-  <si>
-    <t>Davanagere</t>
-  </si>
-  <si>
-    <t>Dharwad</t>
-  </si>
-  <si>
-    <t>Gadag</t>
-  </si>
-  <si>
-    <t>Kalaburagi</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>Haveri</t>
-  </si>
-  <si>
-    <t>Kodagu</t>
-  </si>
-  <si>
-    <t>Kolar</t>
-  </si>
-  <si>
-    <t>Koppal</t>
-  </si>
-  <si>
-    <t>Mandya</t>
-  </si>
-  <si>
-    <t>Mysuru</t>
-  </si>
-  <si>
-    <t>Raichur</t>
-  </si>
-  <si>
-    <t>Ramanagara</t>
-  </si>
-  <si>
-    <t>Shivamogga</t>
-  </si>
-  <si>
-    <t>Tumakuru</t>
-  </si>
-  <si>
-    <t>Udupi</t>
-  </si>
-  <si>
-    <t>Uttara Kannada</t>
-  </si>
-  <si>
-    <t>Vijayanagar</t>
-  </si>
-  <si>
-    <t>Yadgir</t>
+    <t>bagalkot</t>
+  </si>
+  <si>
+    <t>bengaluru rural</t>
+  </si>
+  <si>
+    <t>bengaluru urban</t>
+  </si>
+  <si>
+    <t>belagavi</t>
+  </si>
+  <si>
+    <t>ballari</t>
+  </si>
+  <si>
+    <t>bidar</t>
+  </si>
+  <si>
+    <t>vijayapura</t>
+  </si>
+  <si>
+    <t>chamarajanagara</t>
+  </si>
+  <si>
+    <t>chikkaballapura</t>
+  </si>
+  <si>
+    <t>chikkamagaluru</t>
+  </si>
+  <si>
+    <t>chitradurga</t>
+  </si>
+  <si>
+    <t>dakshina kannada</t>
+  </si>
+  <si>
+    <t>davanagere</t>
+  </si>
+  <si>
+    <t>dharwad</t>
+  </si>
+  <si>
+    <t>gadag</t>
+  </si>
+  <si>
+    <t>kalaburgi</t>
+  </si>
+  <si>
+    <t>hassan</t>
+  </si>
+  <si>
+    <t>haveri</t>
+  </si>
+  <si>
+    <t>kodagu</t>
+  </si>
+  <si>
+    <t>kolar</t>
+  </si>
+  <si>
+    <t>koppal</t>
+  </si>
+  <si>
+    <t>mandya</t>
+  </si>
+  <si>
+    <t>mysuru</t>
+  </si>
+  <si>
+    <t>raichur</t>
+  </si>
+  <si>
+    <t>ramanagara</t>
+  </si>
+  <si>
+    <t>tumakuru</t>
+  </si>
+  <si>
+    <t>udupi</t>
+  </si>
+  <si>
+    <t>uttara kannada sirsi</t>
+  </si>
+  <si>
+    <t>vijayanagar</t>
+  </si>
+  <si>
+    <t>yadagiri</t>
+  </si>
+  <si>
+    <t>shivamogga</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Computer Available</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -546,9 +552,11 @@
     <col min="17" max="17" width="20.44140625" customWidth="1"/>
     <col min="18" max="18" width="22.109375" customWidth="1"/>
     <col min="19" max="19" width="20.88671875" customWidth="1"/>
+    <col min="20" max="20" width="25.44140625" customWidth="1"/>
+    <col min="21" max="21" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -609,8 +617,14 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -671,10 +685,16 @@
       <c r="T2">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2">
+        <v>752</v>
+      </c>
+      <c r="V2">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>760362</v>
@@ -733,10 +753,16 @@
       <c r="T3">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3">
+        <v>4273</v>
+      </c>
+      <c r="V3">
+        <v>5289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>291083</v>
@@ -795,8 +821,14 @@
       <c r="T4">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4">
+        <v>394</v>
+      </c>
+      <c r="V4">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -857,8 +889,14 @@
       <c r="T5">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5">
+        <v>636</v>
+      </c>
+      <c r="V5">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -919,8 +957,14 @@
       <c r="T6">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6">
+        <v>453</v>
+      </c>
+      <c r="V6">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -981,8 +1025,14 @@
       <c r="T7">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7">
+        <v>703</v>
+      </c>
+      <c r="V7">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1043,8 +1093,14 @@
       <c r="T8">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8">
+        <v>999</v>
+      </c>
+      <c r="V8">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1105,8 +1161,14 @@
       <c r="T9">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9">
+        <v>251</v>
+      </c>
+      <c r="V9">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1167,8 +1229,14 @@
       <c r="T10">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10">
+        <v>346</v>
+      </c>
+      <c r="V10">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1229,8 +1297,14 @@
       <c r="T11">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U11">
+        <v>407</v>
+      </c>
+      <c r="V11">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1291,8 +1365,14 @@
       <c r="T12">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U12">
+        <v>442</v>
+      </c>
+      <c r="V12">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1353,8 +1433,14 @@
       <c r="T13">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U13">
+        <v>909</v>
+      </c>
+      <c r="V13">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1415,8 +1501,14 @@
       <c r="T14">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U14">
+        <v>567</v>
+      </c>
+      <c r="V14">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1477,8 +1569,14 @@
       <c r="T15">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U15">
+        <v>606</v>
+      </c>
+      <c r="V15">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1539,8 +1637,14 @@
       <c r="T16">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U16">
+        <v>876</v>
+      </c>
+      <c r="V16">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1601,8 +1705,14 @@
       <c r="T17">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U17">
+        <v>1077</v>
+      </c>
+      <c r="V17">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1663,8 +1773,14 @@
       <c r="T18">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U18">
+        <v>635</v>
+      </c>
+      <c r="V18">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1725,8 +1841,14 @@
       <c r="T19">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U19">
+        <v>451</v>
+      </c>
+      <c r="V19">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1787,8 +1909,14 @@
       <c r="T20">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U20">
+        <v>224</v>
+      </c>
+      <c r="V20">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1846,8 +1974,14 @@
       <c r="T21">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U21">
+        <v>471</v>
+      </c>
+      <c r="V21">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1908,8 +2042,14 @@
       <c r="T22">
         <v>58</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U22">
+        <v>498</v>
+      </c>
+      <c r="V22">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1970,8 +2110,14 @@
       <c r="T23">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U23">
+        <v>526</v>
+      </c>
+      <c r="V23">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -2032,8 +2178,14 @@
       <c r="T24">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U24">
+        <v>990</v>
+      </c>
+      <c r="V24">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -2094,8 +2246,14 @@
       <c r="T25">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U25">
+        <v>560</v>
+      </c>
+      <c r="V25">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -2156,10 +2314,16 @@
       <c r="T26">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U26">
+        <v>374</v>
+      </c>
+      <c r="V26">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B27">
         <v>290893</v>
@@ -2218,10 +2382,16 @@
       <c r="T27">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U27">
+        <v>801</v>
+      </c>
+      <c r="V27">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28">
         <v>245735</v>
@@ -2280,10 +2450,16 @@
       <c r="T28">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U28">
+        <v>585</v>
+      </c>
+      <c r="V28">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29">
         <v>414274</v>
@@ -2342,10 +2518,16 @@
       <c r="T29">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U29">
+        <v>461</v>
+      </c>
+      <c r="V29">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30">
         <v>220984</v>
@@ -2404,10 +2586,16 @@
       <c r="T30">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U30">
+        <v>219</v>
+      </c>
+      <c r="V30">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31">
         <v>159868</v>
@@ -2454,10 +2642,16 @@
       <c r="T31">
         <v>31</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U31">
+        <v>410</v>
+      </c>
+      <c r="V31">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32">
         <v>153247</v>
@@ -2515,6 +2709,12 @@
       </c>
       <c r="T32">
         <v>44</v>
+      </c>
+      <c r="U32">
+        <v>324</v>
+      </c>
+      <c r="V32">
+        <v>819</v>
       </c>
     </row>
   </sheetData>
